--- a/make_table/tuikuan/t1.xlsx
+++ b/make_table/tuikuan/t1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>申请日期</t>
   </si>
@@ -59,232 +59,124 @@
     <t>腾伟</t>
   </si>
   <si>
-    <t>5112541586180006046</t>
-  </si>
-  <si>
-    <t>ucss2003</t>
-  </si>
-  <si>
-    <t>申通快递 772061368381637</t>
-  </si>
-  <si>
-    <t>0502物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>5112752654517270332</t>
-  </si>
-  <si>
-    <t>miaoshou回春32</t>
-  </si>
-  <si>
-    <t>京东快递 JDX053261121983</t>
-  </si>
-  <si>
-    <r>
-      <t>3298881036207024386</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3298293410900024386</t>
-    </r>
-  </si>
-  <si>
-    <t>随便取个名11214751</t>
-  </si>
-  <si>
-    <t>顾客取消</t>
-  </si>
-  <si>
-    <t>5112505190676074648</t>
-  </si>
-  <si>
-    <t>waiab</t>
-  </si>
-  <si>
-    <t>申通快递 772061348584296</t>
-  </si>
-  <si>
-    <t>5112774578033004030</t>
-  </si>
-  <si>
-    <t>窈窈水含笑_2008</t>
-  </si>
-  <si>
-    <t>申通快递 772061345605363</t>
-  </si>
-  <si>
-    <t>0501物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>5111591907866018935</t>
-  </si>
-  <si>
-    <t>yuan男人</t>
-  </si>
-  <si>
-    <t>申通快递 772061319219952</t>
-  </si>
-  <si>
-    <t>5112580285384016149</t>
-  </si>
-  <si>
-    <t>tttwoa</t>
-  </si>
-  <si>
-    <t>申通快递 772061326293122</t>
-  </si>
-  <si>
-    <t>5111452335942020120</t>
-  </si>
-  <si>
-    <t>donghaiqiang19880726</t>
-  </si>
-  <si>
-    <t>申通快递 772061226028419</t>
-  </si>
-  <si>
-    <t>0430物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>梓越</t>
-  </si>
-  <si>
-    <t>3297905761714027877</t>
-  </si>
-  <si>
-    <t>罗凯瑞1999</t>
-  </si>
-  <si>
-    <t>中通快递 73706275175725</t>
+    <t>3300997514692025890</t>
+  </si>
+  <si>
+    <t>mn9597</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5136702076003</t>
+  </si>
+  <si>
+    <t>0515物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>瑞丰</t>
+  </si>
+  <si>
+    <t>5115035127661083437</t>
+  </si>
+  <si>
+    <t>ningxu78</t>
+  </si>
+  <si>
+    <t>暂未寄出</t>
+  </si>
+  <si>
+    <t>5115356462549013324</t>
+  </si>
+  <si>
+    <t>一壹壹壹壹壹</t>
+  </si>
+  <si>
+    <t>EMS 1397879895933</t>
+  </si>
+  <si>
+    <t>5115403658205016604</t>
+  </si>
+  <si>
+    <t>wk18767181892</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5136512448933</t>
+  </si>
+  <si>
+    <t>0514物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>5115363336366017346</t>
+  </si>
+  <si>
+    <t>sophiatea7855</t>
+  </si>
+  <si>
+    <t>申通快递 772062749864806</t>
+  </si>
+  <si>
+    <t>5115663612966008047</t>
+  </si>
+  <si>
+    <t>芦芦坊</t>
+  </si>
+  <si>
+    <t>中通快递 73708363818611</t>
+  </si>
+  <si>
+    <t>换货</t>
+  </si>
+  <si>
+    <t>5114704502680001518</t>
+  </si>
+  <si>
+    <t>我想牵着你的手v</t>
+  </si>
+  <si>
+    <t>中通快递 73708339400067</t>
+  </si>
+  <si>
+    <t>3300997116641078451</t>
+  </si>
+  <si>
+    <t>cenxu7007</t>
+  </si>
+  <si>
+    <t>申通快递 772062687733075</t>
+  </si>
+  <si>
+    <t>3300739898551029157</t>
+  </si>
+  <si>
+    <t>马勇山</t>
+  </si>
+  <si>
+    <t>申通快递 772062536610159</t>
+  </si>
+  <si>
+    <t>0513物流已更新到潮州</t>
   </si>
   <si>
     <t>是</t>
   </si>
   <si>
-    <t>3298624789787020998</t>
-  </si>
-  <si>
-    <t>快乐兔子999200</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0223964041105</t>
-  </si>
-  <si>
-    <t>5112623268640147926</t>
-  </si>
-  <si>
-    <t>yppno1</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5190341753928</t>
-  </si>
-  <si>
-    <t>0430物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>5112453747049074013</t>
-  </si>
-  <si>
-    <t>哈哈嘻chm</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5131196350946</t>
-  </si>
-  <si>
-    <t>0429物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>3298385497840145791</t>
-  </si>
-  <si>
-    <t>嘉合宝贝</t>
-  </si>
-  <si>
-    <t>中通快递 73706190057375</t>
-  </si>
-  <si>
-    <t>3298389531362044479</t>
-  </si>
-  <si>
-    <t>tb651964442493</t>
-  </si>
-  <si>
-    <t>SF5131022766781</t>
-  </si>
-  <si>
-    <t>5111094925001027547</t>
-  </si>
-  <si>
-    <t>tb942192175</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3161329705289</t>
-  </si>
-  <si>
-    <t>0429物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>5112297722999098522</t>
-  </si>
-  <si>
-    <t>t_1484586471144_0593</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5131080598864</t>
-  </si>
-  <si>
-    <r>
-      <t>3297745059469031588</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3298360800888004760</t>
-    </r>
-  </si>
-  <si>
-    <t>hsinhsia820</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5131064721716</t>
-  </si>
-  <si>
-    <t>5111927029757048016</t>
-  </si>
-  <si>
-    <t>占明1030</t>
-  </si>
-  <si>
-    <t>申通快递 772061112069930</t>
+    <t>5115377736942050732</t>
+  </si>
+  <si>
+    <t>bffymyq</t>
+  </si>
+  <si>
+    <t>申通快递 772062540631547</t>
+  </si>
+  <si>
+    <t>5114123499802013647</t>
+  </si>
+  <si>
+    <t>maartenigel</t>
+  </si>
+  <si>
+    <t>772062623195575</t>
+  </si>
+  <si>
+    <t>0513物流未更新到潮州</t>
   </si>
 </sst>
 </file>
@@ -340,8 +232,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFDE3C36"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -352,12 +250,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="PingFang SC"/>
@@ -365,7 +257,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFDE3C36"/>
+      <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -989,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1001,76 +893,100 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1146,13 +1062,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:colOff>289560</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="图片 34"/>
+        <xdr:cNvPr id="2" name="图片 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1166,7 +1082,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4076700" y="182880"/>
-          <a:ext cx="1508760" cy="228600"/>
+          <a:ext cx="1524000" cy="274320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1190,11 +1106,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="图片 35"/>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1208,7 +1124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4076700" y="373380"/>
-          <a:ext cx="1524000" cy="228600"/>
+          <a:ext cx="1524000" cy="274320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1230,13 +1146,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="图片 36"/>
+        <xdr:cNvPr id="4" name="图片 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1250,7 +1166,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4076700" y="563880"/>
-          <a:ext cx="1516380" cy="525780"/>
+          <a:ext cx="1508760" cy="350520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1274,11 +1190,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="图片 37"/>
+        <xdr:cNvPr id="5" name="图片 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1291,8 +1207,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="853440"/>
-          <a:ext cx="1524000" cy="228600"/>
+          <a:off x="4076700" y="754380"/>
+          <a:ext cx="1524000" cy="289560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1315,12 +1231,12 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="图片 38"/>
+        <xdr:cNvPr id="6" name="图片 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1333,8 +1249,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1043940"/>
-          <a:ext cx="1524000" cy="701040"/>
+          <a:off x="4076700" y="944880"/>
+          <a:ext cx="1524000" cy="243840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1362,7 +1278,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="图片 39"/>
+        <xdr:cNvPr id="7" name="图片 6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1375,7 +1291,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1234440"/>
+          <a:off x="4076700" y="1135380"/>
           <a:ext cx="1524000" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1398,13 +1314,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
+      <xdr:colOff>289560</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="图片 40"/>
+        <xdr:cNvPr id="8" name="图片 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1417,8 +1333,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1424940"/>
-          <a:ext cx="1516380" cy="274320"/>
+          <a:off x="4076700" y="1325880"/>
+          <a:ext cx="1524000" cy="220980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1442,11 +1358,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="图片 41"/>
+        <xdr:cNvPr id="9" name="图片 8"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1459,8 +1375,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1615440"/>
-          <a:ext cx="1524000" cy="236220"/>
+          <a:off x="4076700" y="1516380"/>
+          <a:ext cx="1524000" cy="297180"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1484,11 +1400,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="图片 42"/>
+        <xdr:cNvPr id="10" name="图片 9"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1501,8 +1417,50 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1805940"/>
-          <a:ext cx="1524000" cy="274320"/>
+          <a:off x="4076700" y="1706880"/>
+          <a:ext cx="1524000" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>54610</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9083040" y="1706880"/>
+          <a:ext cx="3048000" cy="237490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1526,25 +1484,67 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="图片 43"/>
+        <xdr:cNvPr id="12" name="图片 11"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
+        <a:blip r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="1996440"/>
-          <a:ext cx="1524000" cy="297180"/>
+          <a:off x="4076700" y="1889760"/>
+          <a:ext cx="1524000" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>19685</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="图片 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9083040" y="1889760"/>
+          <a:ext cx="3048000" cy="202565"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1568,25 +1568,25 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>289560</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="图片 44"/>
+        <xdr:cNvPr id="14" name="图片 13"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="2186940"/>
-          <a:ext cx="1524000" cy="274320"/>
+          <a:off x="4076700" y="2072640"/>
+          <a:ext cx="1524000" cy="281940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1607,98 +1607,14 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>481965</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>170815</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>136525</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="图片 45"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9083040" y="2186940"/>
-          <a:ext cx="2333625" cy="170815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="图片 46"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="2369820"/>
-          <a:ext cx="1524000" cy="266700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="图片 47"/>
+        <xdr:cNvPr id="15" name="图片 14"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1711,302 +1627,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4076700" y="2560320"/>
-          <a:ext cx="1524000" cy="259080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="图片 48"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="2750820"/>
-          <a:ext cx="1516380" cy="236220"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="图片 49"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="2941320"/>
-          <a:ext cx="1524000" cy="274320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="图片 50"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="3131820"/>
-          <a:ext cx="1508760" cy="281940"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>442595</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>104140</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="图片 51"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9083040" y="3131820"/>
-          <a:ext cx="2294255" cy="287020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="图片 52"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="3314700"/>
-          <a:ext cx="1524000" cy="525780"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>481965</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>64135</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="图片 53"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9083040" y="3314700"/>
-          <a:ext cx="2333625" cy="353695"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="图片 54"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4076700" y="3604260"/>
-          <a:ext cx="1508760" cy="236220"/>
+          <a:off x="9083040" y="2072640"/>
+          <a:ext cx="2605405" cy="417830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2348,7 +1970,7 @@
     </row>
     <row r="2" ht="15" spans="2:12">
       <c r="B2" s="2">
-        <v>46144</v>
+        <v>46157</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -2361,7 +1983,7 @@
       </c>
       <c r="F2"/>
       <c r="G2" s="6">
-        <v>112</v>
+        <v>157.12</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>12</v>
@@ -2371,819 +1993,712 @@
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="9"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" ht="15" spans="2:12">
       <c r="B3" s="2">
-        <v>46144</v>
+        <v>46156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3"/>
       <c r="G3" s="6">
-        <v>99.2</v>
+        <v>154</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>13</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="J3" s="8"/>
       <c r="K3" s="9"/>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" ht="22.8" spans="2:12">
-      <c r="B4" s="11">
-        <v>46144</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="14" t="s">
+    <row r="4" ht="15" spans="2:12">
+      <c r="B4" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>18</v>
       </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="F4"/>
-      <c r="G4" s="15">
-        <v>2567.34</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="5"/>
+      <c r="G4" s="6">
+        <v>838</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="J4" s="8"/>
       <c r="K4" s="9"/>
       <c r="L4" s="10"/>
     </row>
     <row r="5" ht="15" spans="2:12">
       <c r="B5" s="2">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
+      <c r="D5" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5"/>
       <c r="G5" s="6">
-        <v>97.92</v>
+        <v>1394.2</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="9"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" ht="15" spans="2:12">
       <c r="B6" s="2">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>23</v>
+      <c r="D6" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6"/>
       <c r="G6" s="6">
-        <v>395.2</v>
+        <v>154</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="9"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" ht="15" spans="2:12">
       <c r="B7" s="2">
-        <v>46143</v>
+        <v>46156</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
+      <c r="D7" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7"/>
       <c r="G7" s="6">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="K7" s="9"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" ht="15" spans="2:12">
       <c r="B8" s="2">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>30</v>
+      <c r="D8" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8"/>
       <c r="G8" s="6">
-        <v>144.32</v>
+        <v>152.12</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" ht="15" spans="2:12">
       <c r="B9" s="2">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="F9"/>
       <c r="G9" s="6">
-        <v>827.12</v>
+        <v>125.09</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="9"/>
-    </row>
-    <row r="10" ht="15" spans="2:12">
-      <c r="B10" s="2">
-        <v>46141</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="12">
+        <v>46154</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="15" t="s">
         <v>39</v>
       </c>
       <c r="F10"/>
-      <c r="G10" s="6">
-        <v>776.7</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="16">
+        <v>140.2</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" ht="15" spans="2:12">
-      <c r="B11" s="2">
-        <v>46141</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="J10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="12">
+        <v>46154</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>43</v>
       </c>
+      <c r="E11" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="F11"/>
-      <c r="G11" s="6">
-        <v>1919.67</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
+      <c r="G11" s="16">
+        <v>138.32</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="11">
-        <v>46141</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="12">
+        <v>46154</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>45</v>
+      <c r="D12" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12"/>
-      <c r="G12" s="15">
-        <v>163.12</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="14" t="s">
+      <c r="G12" s="16">
+        <v>769.21</v>
+      </c>
+      <c r="H12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="20"/>
+      <c r="I12" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" ht="15" spans="2:12">
-      <c r="B13" s="11">
-        <v>46141</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13"/>
-      <c r="G13" s="15">
-        <v>1262.45</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="9"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="28"/>
     </row>
     <row r="14" ht="15" spans="2:12">
-      <c r="B14" s="2">
-        <v>46141</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14"/>
-      <c r="G14" s="6">
-        <v>927.01</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="9"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" ht="15" spans="2:12">
-      <c r="B15" s="2">
-        <v>46141</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15"/>
-      <c r="G15" s="6">
-        <v>1284.2</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="9"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="28"/>
     </row>
     <row r="16" ht="15" spans="2:12">
-      <c r="B16" s="2">
-        <v>46140</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16"/>
-      <c r="G16" s="6">
-        <v>110</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="9"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="32"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="28"/>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="11">
-        <v>46140</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17"/>
-      <c r="G17" s="15">
-        <v>1699</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="19"/>
-    </row>
-    <row r="18" ht="22.8" spans="2:11">
-      <c r="B18" s="11">
-        <v>46140</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18"/>
-      <c r="G18" s="15">
-        <v>3736.84</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="36"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="36"/>
     </row>
     <row r="19" ht="15" spans="2:11">
-      <c r="B19" s="2">
-        <v>46140</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19" s="6">
-        <v>526.04</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="9"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="28"/>
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
       <c r="D20" s="23"/>
-      <c r="E20" s="10"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
+      <c r="E20" s="24"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="36"/>
     </row>
     <row r="21" ht="15" spans="2:11">
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="10"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="27"/>
+      <c r="E21" s="24"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="28"/>
     </row>
     <row r="22" ht="15" spans="2:11">
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
       <c r="D22" s="23"/>
-      <c r="E22" s="10"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="27"/>
+      <c r="E22" s="24"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="28"/>
     </row>
     <row r="23" ht="15" spans="2:11">
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
       <c r="D23" s="23"/>
-      <c r="E23" s="10"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="27"/>
+      <c r="E23" s="24"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="28"/>
     </row>
     <row r="24" ht="15" spans="2:11">
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="10"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="27"/>
+      <c r="E24" s="24"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="28"/>
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
       <c r="D25" s="23"/>
-      <c r="E25" s="10"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="26"/>
+      <c r="E25" s="24"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="36"/>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
       <c r="D26" s="23"/>
-      <c r="E26" s="10"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
+      <c r="E26" s="24"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="36"/>
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
       <c r="D27" s="23"/>
-      <c r="E27" s="10"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="26"/>
+      <c r="E27" s="24"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="36"/>
     </row>
     <row r="28" ht="15" spans="2:11">
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="10"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="27"/>
+      <c r="E28" s="24"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="28"/>
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="10"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="24"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="36"/>
     </row>
     <row r="30" ht="15" spans="2:11">
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="10"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="27"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="24"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="28"/>
     </row>
     <row r="31" ht="15" spans="2:11">
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="10"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="27"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="24"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="28"/>
     </row>
     <row r="32" ht="15" spans="2:11">
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="10"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="24"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="28"/>
     </row>
     <row r="33" spans="2:11">
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="10"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="24"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="36"/>
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="10"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="24"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="36"/>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="10"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="24"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="36"/>
     </row>
     <row r="36" ht="15" spans="2:11">
       <c r="B36" s="21"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="10"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="27"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="24"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="28"/>
     </row>
     <row r="37" ht="15" spans="2:11">
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="10"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="27"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="24"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="28"/>
     </row>
     <row r="38" ht="15" spans="2:11">
       <c r="B38" s="21"/>
       <c r="C38" s="22"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="10"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="27"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="24"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="10"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="24"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="36"/>
     </row>
     <row r="40" ht="15" spans="2:11">
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="10"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="27"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="24"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="28"/>
     </row>
     <row r="41" ht="15" spans="2:11">
       <c r="B41" s="21"/>
       <c r="C41" s="22"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="10"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="27"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="24"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="28"/>
     </row>
     <row r="42" ht="15" spans="2:11">
       <c r="B42" s="21"/>
       <c r="C42" s="22"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="10"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="27"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="24"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="28"/>
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="21"/>
       <c r="C43" s="22"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="10"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="24"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="36"/>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="10"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="24"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="36"/>
     </row>
     <row r="45" ht="15" spans="2:11">
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="10"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="27"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="24"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="27"/>
+      <c r="K45" s="28"/>
     </row>
     <row r="46" ht="15" spans="2:11">
       <c r="B46" s="21"/>
       <c r="C46" s="22"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="10"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="27"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="24"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="27"/>
+      <c r="K46" s="28"/>
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="21"/>
       <c r="C47" s="22"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="10"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="25"/>
-      <c r="K47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="24"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="27"/>
+      <c r="K47" s="36"/>
     </row>
     <row r="48" spans="2:11">
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="10"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="25"/>
-      <c r="K48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="24"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="36"/>
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="10"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="24"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="36"/>
     </row>
     <row r="50" ht="15" spans="2:11">
       <c r="B50" s="21"/>
       <c r="C50" s="22"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="10"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="25"/>
-      <c r="K50" s="27"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="24"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="27"/>
+      <c r="K50" s="28"/>
     </row>
     <row r="51" spans="2:11">
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="10"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="24"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="27"/>
+      <c r="K51" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
